--- a/artfynd/A 63190-2023 artfynd.xlsx
+++ b/artfynd/A 63190-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63190-2023 artfynd.xlsx
+++ b/artfynd/A 63190-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>121245693</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>121245704</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2023 artfynd.xlsx
+++ b/artfynd/A 63190-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121245693</v>
+        <v>121245704</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>57720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,33 +800,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -884,21 +879,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Morän</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Moraine</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -915,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121245704</v>
+        <v>121245693</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,28 +907,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1006,6 +991,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Morän</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Moraine</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 63190-2023 artfynd.xlsx
+++ b/artfynd/A 63190-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>121245704</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>121245693</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2023 artfynd.xlsx
+++ b/artfynd/A 63190-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121245704</v>
+        <v>121245693</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,28 +800,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -879,6 +884,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Morän</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Moraine</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -895,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121245693</v>
+        <v>121245704</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57723</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,33 +927,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -991,21 +1006,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Morän</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Moraine</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 63190-2023 artfynd.xlsx
+++ b/artfynd/A 63190-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>121245693</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>121245704</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57724</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2023 artfynd.xlsx
+++ b/artfynd/A 63190-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>121245693</v>
       </c>
       <c r="B3" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>121245704</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>57725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2023 artfynd.xlsx
+++ b/artfynd/A 63190-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121245693</v>
+        <v>121245704</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>57725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,33 +800,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -884,21 +879,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Morän</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Moraine</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -915,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121245704</v>
+        <v>121245693</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,28 +907,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1006,6 +991,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Morän</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Moraine</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 63190-2023 artfynd.xlsx
+++ b/artfynd/A 63190-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121245704</v>
+        <v>121245693</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,28 +800,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -879,6 +884,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Morän</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Moraine</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -895,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121245693</v>
+        <v>121245704</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>57725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,33 +927,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -991,21 +1006,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Morän</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Moraine</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
